--- a/01-foundations/05-cell-references/1.5-cell-references.xlsx
+++ b/01-foundations/05-cell-references/1.5-cell-references.xlsx
@@ -783,7 +783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C35"/>
+  <dimension ref="B1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -791,6 +791,7 @@
     <col width="95" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -812,6 +813,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -868,6 +870,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -956,87 +959,89 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Staffing Grid, Q4 Summary, and Plan 2026 are layout sheets with yellow grids for you to fill with one formula each.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Keep the Oct, Nov, and Dec tabs together and in that order: 3-D formulas depend on tab positions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+          <t>Keep the Oct, Nov, and Dec tabs together and in that order, because 3-D formulas depend on tab positions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Color legend</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Yellow cell</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Your answer goes here.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Yellow cell</t>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Gray cell</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Your answer goes here.</t>
+          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Gray cell</t>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>✔ Correct</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Your answer matches the key.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>✔ Correct</t>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>✘ Not yet</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Your answer matches the key.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>✘ Not yet</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
           <t>Not matching yet — check the hint and try again.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Sheets in this workbook</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
+      <c r="C27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>12 tasks. Type answers in the yellow cells. Gray cells check work you do on the other sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Expenses</t>
@@ -1044,77 +1049,101 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 17 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
+          <t>Bluestone Memorial's 2025 operating expense: 16 departments (rows 5–20) × 7 categories (columns C–I), with totals in column J and row 21. You fill the yellow % of Total column K (task 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>4 West OT</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 17 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
+          <t>December 2025 overtime for 67 hourly staff on Medical-Surgical 4 West, with the overtime multiplier in B3. You fill the yellow OTPay column H (tasks 5–7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="33" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Staffing Grid</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 17 rows</t>
+          <t>Census values down column A × HPPD targets across row 5. You fill the yellow grid with one formula (task 9).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Q4 Summary</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 17 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
+          <t>Same layout as Oct, Nov, and Dec. You fill the yellow grid with one 3-D formula (task 11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>4 West OT</t>
+          <t>Oct · Nov · Dec</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 67 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="48" customHeight="1">
+          <t>Monthly actuals for October, November, and December 2025, in the same layout as Expenses (tasks 10–12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>5 harder tasks that build and test a 2026 expense plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="33" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Plan 2026</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>The 2026 plan, with blue planning assumptions: price inflation in row 3 and volume growth in column B. You fill the yellow grid with one formula (bonus task B1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t>About the data</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Bluestone Memorial Hospital's 2025 operating expenses by department and category, the same breakdown for October, November, and December 2025, December 2025 overtime for the hourly staff of Medical-Surgical 4 West, and a 4 West staffing grid.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -1205,7 +1234,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Fill the yellow grid on the Plan 2026 sheet (C5:I20) with ONE formula typed in C5 and copied across and down. The gray cell adds up your grid: what is the 2026 plan total? (Don't round.)</t>
+          <t>Fill the yellow grid on the Plan 2026 sheet (C5:I20) with ONE formula typed in C5 and copied across and down. The gray cell adds up your grid: what is the 2026 plan total? (Don't round inside the formula.)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -1296,7 +1325,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Pharmaceutical prices are the shakiest assumption. If pharmaceutical inflation were 9.0% instead of 7.5%, how many dollars higher would the 2026 plan total be? Change the one input cell, compare the totals, then put it back. Round to the nearest dollar.</t>
+          <t>Pharmaceutical prices are the shakiest assumption. If pharmaceutical inflation were 9.0% instead of 7.5%, how many dollars higher would the 2026 plan total be? Change the one input cell, compare the totals, and type the difference here as a number, rounded to the nearest dollar. Then put the input back.</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -1361,7 +1390,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>2026 = 2025 actual from the Expenses sheet (same cell) × (1 + price inflation in row 3) × (1 + volume growth in column B). Blue cells are planning assumptions.</t>
+          <t>2026 = 2025 actual from the Expenses sheet (same cell) × (1 + price inflation in row 3) × (1 + volume growth in column B). Blue cells are planning assumptions. Fill the yellow grid with ONE formula typed in C5 (bonus task B1).</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2028,7 @@
       </c>
       <c r="D8" s="58" t="inlineStr">
         <is>
-          <t>F4 cycles C21 → $C$21 → C$21 → $C21 → back to C21. The third press gives **$C21**.</t>
+          <t>F4 cycles C21 → $C$21 → C$21 → $C21 → back to C21. The third press gives $C21.</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -2087,9 +2116,9 @@
       </c>
       <c r="D11" s="58" t="inlineStr">
         <is>
-          <t>1. Click **'4 West OT'!B3**, type `2`, and press **Enter**.
+          <t>1. Click '4 West OT'!B3, type 2, and press Enter.
 2. Read the gray cell in task 6 and type that amount into this task's yellow cell.
-3. Change B3 back to `1.5` so tasks 5 and 6 show ✔ again.</t>
+3. Change B3 back to 1.5 so tasks 5 and 6 show ✔ again.</t>
         </is>
       </c>
       <c r="E11" cm="1" s="62">
@@ -2120,7 +2149,7 @@
       </c>
       <c r="D12" s="58" t="inlineStr">
         <is>
-          <t>The move is 2 columns right (B to D) and 3 rows down (row 3 to row 6). In B$2 the row is locked, so only the column moves and it becomes D$2. In $A3 the column is locked, so only the row moves and it becomes $A6. The answer is **=D$2*$A6**.</t>
+          <t>The move is 2 columns right (B to D) and 3 rows down (row 3 to row 6). In B$2 the row is locked, so only the column moves and it becomes D$2. In $A3 the column is locked, so only the row moves and it becomes $A6. The answer is =D$2*$A6.</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -2221,7 +2250,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="96" customHeight="1">
+    <row r="16" ht="111" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>12</t>
@@ -2229,7 +2258,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>A colleague drags the Nov tab to the right of the Dec tab. What would =SUM(Oct:Dec!J21) return then? (J21 is each month's hospital total.) Predict it with a formula. If you test it by moving the tab, drag Nov back between Oct and Dec afterwards.</t>
+          <t>A colleague drags the Nov tab to the right of the Dec tab. What would =SUM(Oct:Dec!J21) return then? (J21 is each month's hospital total.) Answer with a formula that uses ordinary sheet references, not a 3-D reference, so it stays correct with the tabs in their usual order. If you test the move, drag Nov back between Oct and Dec afterwards.</t>
         </is>
       </c>
       <c r="C16" s="57" t="n">
@@ -2331,7 +2360,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Fill the yellow grid on the Plan 2026 sheet (C5:I20) with ONE formula typed in C5 and copied across and down. The gray cell adds up your grid: what is the 2026 plan total? (Don't round.)</t>
+          <t>Fill the yellow grid on the Plan 2026 sheet (C5:I20) with ONE formula typed in C5 and copied across and down. The gray cell adds up your grid: what is the 2026 plan total? (Don't round inside the formula.)</t>
         </is>
       </c>
       <c r="C5" s="61" t="n">
@@ -2428,8 +2457,8 @@
       </c>
       <c r="D8" s="58" t="inlineStr">
         <is>
-          <t>1. In 'Plan 2026'!K5, type `=J5/Expenses!J5-1` and copy it down to K20. Both references are relative, so each row compares its own department.
-2. Format K5:K20 as a percentage and find the largest value (`=MAX(K5:K20)` helps).
+          <t>1. In 'Plan 2026'!K5, type =J5/Expenses!J5-1 and copy it down to K20. Both references are relative, so each row compares its own department.
+2. Format K5:K20 as a percentage and find the largest value (=MAX(K5:K20) helps).
 3. Read the department name in column A of that row.</t>
         </is>
       </c>
@@ -2444,7 +2473,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="96" customHeight="1">
+    <row r="9" ht="171" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B5</t>
@@ -2452,7 +2481,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Pharmaceutical prices are the shakiest assumption. If pharmaceutical inflation were 9.0% instead of 7.5%, how many dollars higher would the 2026 plan total be? Change the one input cell, compare the totals, then put it back. Round to the nearest dollar.</t>
+          <t>Pharmaceutical prices are the shakiest assumption. If pharmaceutical inflation were 9.0% instead of 7.5%, how many dollars higher would the 2026 plan total be? Change the one input cell, compare the totals, and type the difference here as a number, rounded to the nearest dollar. Then put the input back.</t>
         </is>
       </c>
       <c r="C9" s="64" t="n">
@@ -2460,10 +2489,10 @@
       </c>
       <c r="D9" s="58" t="inlineStr">
         <is>
-          <t>1. Note the plan total in 'Plan 2026'!J21 (or the gray cell in B1).
+          <t>1. Keep a copy of the current plan total: copy 'Plan 2026'!J21 and paste it as a value (Paste Special → Values) into a spare cell such as 'Plan 2026'!L21.
 2. Change 'Plan 2026'!F3 from 7.5% to 9.0%.
-3. Subtract the old total from the new one and round to the nearest dollar.
-4. Set F3 back to 7.5%.</t>
+3. Subtract the old total from the new one (=J21-L21 on Plan 2026), round to the nearest dollar, and type that number into this task's yellow cell.
+4. Set F3 back to 7.5% so B1 and B3 show ✔ again.</t>
         </is>
       </c>
       <c r="E9" cm="1" s="65">
@@ -2472,7 +2501,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>Only the Pharmaceuticals column reads that input, so only those 16 cells change. Each one rises by its 2025 amount × (1 + growth) × 1.5 percentage points. Testing the shakiest assumption like this is called a sensitivity check, and it only takes seconds because the assumption lives in one cell.</t>
+          <t>Only the Pharmaceuticals column reads that input, so only those 16 cells change. Each one rises by its 2025 amount × (1 + growth) × 0.015, which is the 1.5-point rise in the rate. Testing the shakiest assumption like this is called a sensitivity check, and it only takes seconds because the assumption lives in one cell.</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2839,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="66" customHeight="1">
+    <row r="17" ht="81" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>12</t>
@@ -2818,7 +2847,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>A colleague drags the Nov tab to the right of the Dec tab. What would =SUM(Oct:Dec!J21) return then? (J21 is each month's hospital total.) Predict it with a formula. If you test it by moving the tab, drag Nov back between Oct and Dec afterwards.</t>
+          <t>A colleague drags the Nov tab to the right of the Dec tab. What would =SUM(Oct:Dec!J21) return then? (J21 is each month's hospital total.) Answer with a formula that uses ordinary sheet references, not a 3-D reference, so it stays correct with the tabs in their usual order. If you test the move, drag Nov back between Oct and Dec afterwards.</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -3579,10 +3608,10 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>

--- a/01-foundations/05-cell-references/1.5-cell-references.xlsx
+++ b/01-foundations/05-cell-references/1.5-cell-references.xlsx
@@ -246,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -312,10 +312,10 @@
     <xf numFmtId="4" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -355,9 +355,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -382,9 +379,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1065,7 +1059,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="33" customHeight="1">
+    <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Staffing Grid</t>
@@ -1089,7 +1083,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="33" customHeight="1">
+    <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Oct · Nov · Dec</t>
@@ -1333,7 +1327,7 @@
           <t>Because of the $ signs, one edit flows to all 16 Pharmaceuticals cells</t>
         </is>
       </c>
-      <c r="D10" s="52" t="n"/>
+      <c r="D10" s="28" t="n"/>
       <c r="E10" s="22">
         <f>IF(IFERROR(D10="",FALSE),"",IF(IFERROR(AND(ISNUMBER(D10),OR(ABS(D10-'Bonus Key'!$C$9)&lt;=1)),FALSE),"✔ Correct","✘ Not yet"))</f>
         <v/>
@@ -1390,7 +1384,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>2026 = 2025 actual from the Expenses sheet (same cell) × (1 + price inflation in row 3) × (1 + volume growth in column B). Blue cells are planning assumptions. Fill the yellow grid with ONE formula typed in C5 (bonus task B1).</t>
+          <t>2026 = 2025 actual (Expenses sheet, same cell) × (1 + inflation in row 3) × (1 + growth in column B). Blue cells are assumptions. Fill the yellow grid with ONE formula typed in C5 (bonus B1).</t>
         </is>
       </c>
     </row>
@@ -1400,25 +1394,25 @@
           <t>Price inflation →</t>
         </is>
       </c>
-      <c r="C3" s="53" t="n">
+      <c r="C3" s="52" t="n">
         <v>0.035</v>
       </c>
-      <c r="D3" s="53" t="n">
+      <c r="D3" s="52" t="n">
         <v>0.06</v>
       </c>
-      <c r="E3" s="53" t="n">
+      <c r="E3" s="52" t="n">
         <v>0.04</v>
       </c>
-      <c r="F3" s="53" t="n">
+      <c r="F3" s="52" t="n">
         <v>0.075</v>
       </c>
-      <c r="G3" s="53" t="n">
+      <c r="G3" s="52" t="n">
         <v>0.03</v>
       </c>
-      <c r="H3" s="53" t="n">
+      <c r="H3" s="52" t="n">
         <v>0.025</v>
       </c>
-      <c r="I3" s="53" t="n">
+      <c r="I3" s="52" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -1480,7 +1474,7 @@
           <t>Emergency Department</t>
         </is>
       </c>
-      <c r="B5" s="53" t="n">
+      <c r="B5" s="52" t="n">
         <v>0.03</v>
       </c>
       <c r="C5" s="48" t="n"/>
@@ -1501,7 +1495,7 @@
           <t>Medical-Surgical 4 West</t>
         </is>
       </c>
-      <c r="B6" s="53" t="n">
+      <c r="B6" s="52" t="n">
         <v>0.01</v>
       </c>
       <c r="C6" s="48" t="n"/>
@@ -1522,7 +1516,7 @@
           <t>Medical-Surgical 5 East</t>
         </is>
       </c>
-      <c r="B7" s="53" t="n">
+      <c r="B7" s="52" t="n">
         <v>0.005</v>
       </c>
       <c r="C7" s="48" t="n"/>
@@ -1543,7 +1537,7 @@
           <t>Cardiac Step-Down</t>
         </is>
       </c>
-      <c r="B8" s="53" t="n">
+      <c r="B8" s="52" t="n">
         <v>0.02</v>
       </c>
       <c r="C8" s="48" t="n"/>
@@ -1564,7 +1558,7 @@
           <t>Intensive Care Unit</t>
         </is>
       </c>
-      <c r="B9" s="53" t="n">
+      <c r="B9" s="52" t="n">
         <v>0.025</v>
       </c>
       <c r="C9" s="48" t="n"/>
@@ -1585,7 +1579,7 @@
           <t>Orthopedics &amp; Spine</t>
         </is>
       </c>
-      <c r="B10" s="53" t="n">
+      <c r="B10" s="52" t="n">
         <v>0.035</v>
       </c>
       <c r="C10" s="48" t="n"/>
@@ -1606,7 +1600,7 @@
           <t>Oncology</t>
         </is>
       </c>
-      <c r="B11" s="53" t="n">
+      <c r="B11" s="52" t="n">
         <v>0.045</v>
       </c>
       <c r="C11" s="48" t="n"/>
@@ -1627,7 +1621,7 @@
           <t>Neuroscience &amp; Stroke</t>
         </is>
       </c>
-      <c r="B12" s="53" t="n">
+      <c r="B12" s="52" t="n">
         <v>0.035</v>
       </c>
       <c r="C12" s="48" t="n"/>
@@ -1648,7 +1642,7 @@
           <t>Labor &amp; Delivery</t>
         </is>
       </c>
-      <c r="B13" s="53" t="n">
+      <c r="B13" s="52" t="n">
         <v>0.015</v>
       </c>
       <c r="C13" s="48" t="n"/>
@@ -1669,7 +1663,7 @@
           <t>Pediatrics</t>
         </is>
       </c>
-      <c r="B14" s="53" t="n">
+      <c r="B14" s="52" t="n">
         <v>-0.02</v>
       </c>
       <c r="C14" s="48" t="n"/>
@@ -1690,7 +1684,7 @@
           <t>Behavioral Health</t>
         </is>
       </c>
-      <c r="B15" s="53" t="n">
+      <c r="B15" s="52" t="n">
         <v>0.03</v>
       </c>
       <c r="C15" s="48" t="n"/>
@@ -1711,7 +1705,7 @@
           <t>Observation Unit</t>
         </is>
       </c>
-      <c r="B16" s="53" t="n">
+      <c r="B16" s="52" t="n">
         <v>0.05</v>
       </c>
       <c r="C16" s="48" t="n"/>
@@ -1732,7 +1726,7 @@
           <t>Perioperative Services</t>
         </is>
       </c>
-      <c r="B17" s="53" t="n">
+      <c r="B17" s="52" t="n">
         <v>0.04</v>
       </c>
       <c r="C17" s="48" t="n"/>
@@ -1753,7 +1747,7 @@
           <t>Laboratory</t>
         </is>
       </c>
-      <c r="B18" s="53" t="n">
+      <c r="B18" s="52" t="n">
         <v>0.02</v>
       </c>
       <c r="C18" s="48" t="n"/>
@@ -1774,7 +1768,7 @@
           <t>Radiology</t>
         </is>
       </c>
-      <c r="B19" s="53" t="n">
+      <c r="B19" s="52" t="n">
         <v>0.025</v>
       </c>
       <c r="C19" s="48" t="n"/>
@@ -1795,7 +1789,7 @@
           <t>Pharmacy</t>
         </is>
       </c>
-      <c r="B20" s="53" t="n">
+      <c r="B20" s="52" t="n">
         <v>0.03</v>
       </c>
       <c r="C20" s="48" t="n"/>
@@ -1875,46 +1869,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>🔑 Answer Key — Lesson 1.5</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="56" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="56" t="inlineStr">
+      <c r="C4" s="55" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="55" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="55" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="56" t="inlineStr">
+      <c r="F4" s="55" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -1931,12 +1925,12 @@
           <t>On the Expenses sheet, cell J5 contains =SUM(C5:I5), the Emergency Department's total. If you copy J5 and paste it into J14, what formula will J14 contain? Type it without the =, then click J14 to check.</t>
         </is>
       </c>
-      <c r="C5" s="57" t="inlineStr">
+      <c r="C5" s="56" t="inlineStr">
         <is>
           <t>SUM(C14:I14)</t>
         </is>
       </c>
-      <c r="D5" s="58" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>Count the move: from row 5 to row 14 is 9 rows down and 0 columns across. Add 9 to every row number in the formula and leave the column letters alone.</t>
         </is>
@@ -1963,15 +1957,15 @@
           <t>What share of Bluestone Memorial's 2025 operating expense came from the Intensive Care Unit? Divide the ICU's total (Expenses!J9) by the hospital total (Expenses!J21). Enter it as a percentage.</t>
         </is>
       </c>
-      <c r="C6" s="59" t="n">
+      <c r="C6" s="58" t="n">
         <v>0.07469720689953037</v>
       </c>
-      <c r="D6" s="58" t="inlineStr">
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>=Expenses!J9/Expenses!J21</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="60">
+      <c r="E6" cm="1" s="59">
         <f t="array" ref="E6">Expenses!J9/Expenses!J21</f>
         <v/>
       </c>
@@ -1992,15 +1986,15 @@
           <t>On the Expenses sheet, fill the yellow % of Total column (K5:K20) with ONE formula: type it in K5, lock the reference to the hospital total in J21, then drag the fill handle down to row 20. The gray cell adds up your column. If it shows #DIV/0!, the total reference moved when you copied.</t>
         </is>
       </c>
-      <c r="C7" s="59" t="n">
+      <c r="C7" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="58" t="inlineStr">
+      <c r="D7" s="57" t="inlineStr">
         <is>
           <t>=J5/$J$21</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="60">
+      <c r="E7" cm="1" s="59">
         <f t="array" ref="E7">SUM(Expenses!J5:J20)/Expenses!J21</f>
         <v/>
       </c>
@@ -2021,12 +2015,12 @@
           <t>You type =C21 in a cell, leave the cursor in the reference, and press F4 three times (Mac: ⌘ + T three times). Which reference do you end up with? Type it without the =.</t>
         </is>
       </c>
-      <c r="C8" s="57" t="inlineStr">
+      <c r="C8" s="56" t="inlineStr">
         <is>
           <t>$C21</t>
         </is>
       </c>
-      <c r="D8" s="58" t="inlineStr">
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <t>F4 cycles C21 → $C$21 → C$21 → $C21 → back to C21. The third press gives $C21.</t>
         </is>
@@ -2053,15 +2047,15 @@
           <t>On the 4 West OT sheet, Jessica Aguilar (row 33) worked 9.10 overtime hours in December. On this Practice sheet, write a formula for this employee's overtime pay: OTHours × HourlyRate × the overtime multiplier in B3. Refer to the cells; don't type the numbers.</t>
         </is>
       </c>
-      <c r="C9" s="61" t="n">
+      <c r="C9" s="60" t="n">
         <v>559.65</v>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>='4 West OT'!G33*'4 West OT'!D33*'4 West OT'!B3</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="62">
+      <c r="E9" cm="1" s="61">
         <f t="array" ref="E9">'4 West OT'!G33*'4 West OT'!D33*'4 West OT'!B3</f>
         <v/>
       </c>
@@ -2082,15 +2076,15 @@
           <t>On the 4 West OT sheet, fill the yellow OTPay column (H6:H72) with one formula: OTHours × HourlyRate × the overtime multiplier in B3. Type it in H6 and copy it down. The gray cell totals your column: what did December's overtime cost?</t>
         </is>
       </c>
-      <c r="C10" s="61" t="n">
+      <c r="C10" s="60" t="n">
         <v>16029.43245</v>
       </c>
-      <c r="D10" s="58" t="inlineStr">
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>=G6*D6*$B$3</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="62">
+      <c r="E10" cm="1" s="61">
         <f t="array" ref="E10">SUMPRODUCT('4 West OT'!G6:G72,'4 West OT'!D6:D72)*'4 West OT'!B3</f>
         <v/>
       </c>
@@ -2111,17 +2105,17 @@
           <t>Finance asks what December's overtime would have cost at double time. Change '4 West OT'!B3 to 2, read task 6's gray cell, and type that amount here as a number. Then set B3 back to 1.5.</t>
         </is>
       </c>
-      <c r="C11" s="61" t="n">
+      <c r="C11" s="60" t="n">
         <v>21372.5766</v>
       </c>
-      <c r="D11" s="58" t="inlineStr">
+      <c r="D11" s="57" t="inlineStr">
         <is>
           <t>1. Click '4 West OT'!B3, type 2, and press Enter.
 2. Read the gray cell in task 6 and type that amount into this task's yellow cell.
 3. Change B3 back to 1.5 so tasks 5 and 6 show ✔ again.</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="62">
+      <c r="E11" cm="1" s="61">
         <f t="array" ref="E11">SUMPRODUCT('4 West OT'!G6:G72,'4 West OT'!D6:D72)*2</f>
         <v/>
       </c>
@@ -2142,12 +2136,12 @@
           <t>A grid has labels across row 2 and down column A, and cell B3 holds =B$2*$A3. If you copy B3 to D6, what formula will D6 contain? Type it without the =.</t>
         </is>
       </c>
-      <c r="C12" s="57" t="inlineStr">
+      <c r="C12" s="56" t="inlineStr">
         <is>
           <t>D$2*$A6</t>
         </is>
       </c>
-      <c r="D12" s="58" t="inlineStr">
+      <c r="D12" s="57" t="inlineStr">
         <is>
           <t>The move is 2 columns right (B to D) and 3 rows down (row 3 to row 6). In B$2 the row is locked, so only the column moves and it becomes D$2. In $A3 the column is locked, so only the row moves and it becomes $A6. The answer is =D$2*$A6.</t>
         </is>
@@ -2174,10 +2168,10 @@
           <t>On the Staffing Grid sheet, fill the yellow grid B6:H12 with ONE formula: nursing hours needed per day = census (column A) × HPPD target (row 5). Type it in B6, copy it across to H6, then down to row 12. The gray cell adds up the whole grid.</t>
         </is>
       </c>
-      <c r="C13" s="57" t="n">
+      <c r="C13" s="62" t="n">
         <v>13328</v>
       </c>
-      <c r="D13" s="58" t="inlineStr">
+      <c r="D13" s="57" t="inlineStr">
         <is>
           <t>=$A6*B$5</t>
         </is>
@@ -2203,10 +2197,10 @@
           <t>Using one 3-D reference, what did Oncology (row 11 on the Oct, Nov, and Dec sheets) spend on Pharmaceuticals (column F) in Q4 2025?</t>
         </is>
       </c>
-      <c r="C14" s="57" t="n">
+      <c r="C14" s="62" t="n">
         <v>654633</v>
       </c>
-      <c r="D14" s="58" t="inlineStr">
+      <c r="D14" s="57" t="inlineStr">
         <is>
           <t>=SUM(Oct:Dec!F11)</t>
         </is>
@@ -2232,10 +2226,10 @@
           <t>Fill the yellow grid on the Q4 Summary sheet (C5:I20) with ONE 3-D formula that adds the same cell on the Oct, Nov, and Dec sheets. Type it in C5, copy it across to I5, then down to row 20. The gray cell adds up your grid: what was Bluestone Memorial's Q4 operating expense?</t>
         </is>
       </c>
-      <c r="C15" s="57" t="n">
+      <c r="C15" s="62" t="n">
         <v>38299957</v>
       </c>
-      <c r="D15" s="58" t="inlineStr">
+      <c r="D15" s="57" t="inlineStr">
         <is>
           <t>=SUM(Oct:Dec!C5)</t>
         </is>
@@ -2261,10 +2255,10 @@
           <t>A colleague drags the Nov tab to the right of the Dec tab. What would =SUM(Oct:Dec!J21) return then? (J21 is each month's hospital total.) Answer with a formula that uses ordinary sheet references, not a 3-D reference, so it stays correct with the tabs in their usual order. If you test the move, drag Nov back between Oct and Dec afterwards.</t>
         </is>
       </c>
-      <c r="C16" s="57" t="n">
+      <c r="C16" s="62" t="n">
         <v>25941245</v>
       </c>
-      <c r="D16" s="58" t="inlineStr">
+      <c r="D16" s="57" t="inlineStr">
         <is>
           <t>=Oct!J21+Dec!J21</t>
         </is>
@@ -2307,46 +2301,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>🔑 Bonus Key — Lesson 1.5</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="56" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="56" t="inlineStr">
+      <c r="C4" s="55" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="55" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="55" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="56" t="inlineStr">
+      <c r="F4" s="55" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -2363,15 +2357,15 @@
           <t>Fill the yellow grid on the Plan 2026 sheet (C5:I20) with ONE formula typed in C5 and copied across and down. The gray cell adds up your grid: what is the 2026 plan total? (Don't round inside the formula.)</t>
         </is>
       </c>
-      <c r="C5" s="61" t="n">
+      <c r="C5" s="60" t="n">
         <v>162219455.2832</v>
       </c>
-      <c r="D5" s="58" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>=Expenses!C5*(1+C$3)*(1+$B5)</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="62">
+      <c r="E5" cm="1" s="61">
         <f t="array" ref="E5">SUMPRODUCT(Expenses!C5:I20*(1+'Plan 2026'!C3:I3)*(1+'Plan 2026'!B5:B20))</f>
         <v/>
       </c>
@@ -2392,15 +2386,15 @@
           <t>What is the 2026 plan for Laboratory · Medical Supplies (Plan 2026, row 18, column E)? Reference the cell in your grid.</t>
         </is>
       </c>
-      <c r="C6" s="61" t="n">
+      <c r="C6" s="60" t="n">
         <v>3424829.928</v>
       </c>
-      <c r="D6" s="58" t="inlineStr">
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>='Plan 2026'!E18</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="62">
+      <c r="E6" cm="1" s="61">
         <f t="array" ref="E6">Expenses!E18*(1+'Plan 2026'!E3)*(1+'Plan 2026'!B18)</f>
         <v/>
       </c>
@@ -2421,15 +2415,15 @@
           <t>By what percentage would Bluestone Memorial's total operating expense grow from 2025 to 2026 under this plan? Enter it as a percentage.</t>
         </is>
       </c>
-      <c r="C7" s="59" t="n">
+      <c r="C7" s="58" t="n">
         <v>0.06820111893224712</v>
       </c>
-      <c r="D7" s="58" t="inlineStr">
+      <c r="D7" s="57" t="inlineStr">
         <is>
           <t>='Plan 2026'!J21/Expenses!J21-1</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="60">
+      <c r="E7" cm="1" s="59">
         <f t="array" ref="E7">SUMPRODUCT(Expenses!C5:I20*(1+'Plan 2026'!C3:I3)*(1+'Plan 2026'!B5:B20))/Expenses!J21-1</f>
         <v/>
       </c>
@@ -2450,12 +2444,12 @@
           <t>Which department's total expense is planned to grow by the largest percentage? Type the department name exactly as it appears in column A.</t>
         </is>
       </c>
-      <c r="C8" s="57" t="inlineStr">
+      <c r="C8" s="56" t="inlineStr">
         <is>
           <t>Oncology</t>
         </is>
       </c>
-      <c r="D8" s="58" t="inlineStr">
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <t>1. In 'Plan 2026'!K5, type =J5/Expenses!J5-1 and copy it down to K20. Both references are relative, so each row compares its own department.
 2. Format K5:K20 as a percentage and find the largest value (=MAX(K5:K20) helps).
@@ -2484,10 +2478,10 @@
           <t>Pharmaceutical prices are the shakiest assumption. If pharmaceutical inflation were 9.0% instead of 7.5%, how many dollars higher would the 2026 plan total be? Change the one input cell, compare the totals, and type the difference here as a number, rounded to the nearest dollar. Then put the input back.</t>
         </is>
       </c>
-      <c r="C9" s="64" t="n">
+      <c r="C9" s="62" t="n">
         <v>176282</v>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>1. Keep a copy of the current plan total: copy 'Plan 2026'!J21 and paste it as a value (Paste Special → Values) into a spare cell such as 'Plan 2026'!L21.
 2. Change 'Plan 2026'!F3 from 7.5% to 9.0%.
@@ -2495,7 +2489,7 @@
 4. Set F3 back to 7.5% so B1 and B3 show ✔ again.</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="65">
+      <c r="E9" cm="1" s="63">
         <f t="array" ref="E9">ROUND(SUMPRODUCT(Expenses!F5:F20*(1+'Plan 2026'!B5:B20))*(0.09-'Plan 2026'!F3),0)</f>
         <v/>
       </c>

--- a/01-foundations/05-cell-references/1.5-cell-references.xlsx
+++ b/01-foundations/05-cell-references/1.5-cell-references.xlsx
@@ -373,19 +373,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,7 +897,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -905,7 +905,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="64" customHeight="1">
+    <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Finance needs a first-draft 2026 operating expense plan for Bluestone Memorial. The rule: each 2026 cell = the 2025 actual for the same department and category (Expenses sheet) × (1 + that category's price inflation in row 3 of the Plan 2026 sheet) × (1 + that department's volume growth in column B). The Plan 2026 sheet uses the same rows and columns as the Expenses sheet. Column J and row 21 of Plan 2026 already total whatever you put in the grid.</t>
@@ -1864,7 +1864,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1878,7 +1878,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="54" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2310,7 +2310,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="54" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>

--- a/01-foundations/05-cell-references/1.5-cell-references.xlsx
+++ b/01-foundations/05-cell-references/1.5-cell-references.xlsx
@@ -803,7 +803,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Beginner  ·  about 45 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Beginner  ·  about 85 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>

--- a/01-foundations/05-cell-references/1.5-cell-references.xlsx
+++ b/01-foundations/05-cell-references/1.5-cell-references.xlsx
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C37"/>
+  <dimension ref="B1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -893,7 +893,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell. For tasks 3, 6, 9, and 11, fill the yellow cells on the Expenses, 4 West OT, Staffing Grid, or Q4 Summary sheet instead, and the task's gray cell on Practice reads them.</t>
         </is>
       </c>
     </row>
@@ -1086,58 +1086,82 @@
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Oct · Nov · Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Monthly actuals for October, November, and December 2025, in the same layout as Expenses (tasks 10–12).</t>
+          <t>October 2025 actuals, in the same layout as Expenses. The first tab of the Oct:Dec range (tasks 10–12).</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>November 2025 actuals, same layout. Keep this tab between Oct and Dec (tasks 10–12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>December 2025 actuals, same layout. The last tab of the Oct:Dec range (tasks 10–12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t>Bonus</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>5 harder tasks that build and test a 2026 expense plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="33" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>5 harder tasks that build and test a 2026 expense plan on the Plan 2026 sheet. Type your answers here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33" customHeight="1">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Plan 2026</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>The 2026 plan, with blue planning assumptions: price inflation in row 3 and volume growth in column B. You fill the yellow grid with one formula (bonus task B1).</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="48" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
+    <row r="38" ht="48" customHeight="1">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>About the data</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Bluestone Memorial Hospital's 2025 operating expenses by department and category, the same breakdown for October, November, and December 2025, December 2025 overtime for the hourly staff of Medical-Surgical 4 West, and a 4 West staffing grid.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -2799,7 +2823,7 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Type =SUM(, click the Oct tab, Shift+click the Dec tab, then click the cell</t>
+          <t>Type =SUM(, click the Oct tab, Shift + click the Dec tab, then click the cell</t>
         </is>
       </c>
       <c r="D15" s="28" t="n"/>
